--- a/artfynd/A 10676-2022 artfynd.xlsx
+++ b/artfynd/A 10676-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 10676-2022 artfynd.xlsx
+++ b/artfynd/A 10676-2022 artfynd.xlsx
@@ -1368,12 +1368,7 @@
         <v>79864635</v>
       </c>
       <c r="B8" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1402,7 +1397,11 @@
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1410,10 +1409,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>555989.5733167742</v>
+        <v>555990</v>
       </c>
       <c r="R8" t="n">
-        <v>6514802.641588474</v>
+        <v>6514803</v>
       </c>
       <c r="S8" t="n">
         <v>104</v>
@@ -1443,19 +1442,9 @@
           <t>2019-09-10</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2019-09-10</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1838,12 +1827,7 @@
         <v>89159539</v>
       </c>
       <c r="B12" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8450</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1871,17 +1855,21 @@
       <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Häradstorp, Finspång, Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>556077.3975034462</v>
+        <v>556077</v>
       </c>
       <c r="R12" t="n">
-        <v>6514730.258182899</v>
+        <v>6514730</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1911,19 +1899,9 @@
           <t>2020-11-20</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2020-11-20</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 10676-2022 artfynd.xlsx
+++ b/artfynd/A 10676-2022 artfynd.xlsx
@@ -1368,7 +1368,7 @@
         <v>79864635</v>
       </c>
       <c r="B8" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1827,7 +1827,7 @@
         <v>89159539</v>
       </c>
       <c r="B12" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 10676-2022 artfynd.xlsx
+++ b/artfynd/A 10676-2022 artfynd.xlsx
@@ -2604,7 +2604,7 @@
         <v>131740111</v>
       </c>
       <c r="B19" t="n">
-        <v>91910</v>
+        <v>91913</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 10676-2022 artfynd.xlsx
+++ b/artfynd/A 10676-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,55 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>73809514</v>
+        <v>103305058</v>
       </c>
       <c r="B2" t="n">
-        <v>90008</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6031</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tallåsen, Sävsjön, Ög</t>
+          <t>Häradstorp, Finspång, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>555989.5733167742</v>
+        <v>556069</v>
       </c>
       <c r="R2" t="n">
-        <v>6514802.641588474</v>
+        <v>6514712</v>
       </c>
       <c r="S2" t="n">
-        <v>104</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -747,22 +741,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-11-01</t>
+          <t>2022-09-01</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-11-01</t>
+          <t>2022-09-01</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,74 +765,67 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Staffan Carlsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Staffan Carlsson, Torbjörn Blixt, Claud Youssif</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>73809507</v>
+        <v>103304626</v>
       </c>
       <c r="B3" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>5420</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tallåsen, Sävsjön, Ög</t>
+          <t>Finspång, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>555989.5733167742</v>
+        <v>556041</v>
       </c>
       <c r="R3" t="n">
-        <v>6514802.641588474</v>
+        <v>6514667</v>
       </c>
       <c r="S3" t="n">
-        <v>104</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,22 +849,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2018-11-01</t>
+          <t>2022-09-01</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2018-11-01</t>
+          <t>2022-09-01</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,34 +873,28 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Staffan Carlsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Staffan Carlsson, Torbjörn Blixt, Claud Youssif</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>73809512</v>
+        <v>117235212</v>
       </c>
       <c r="B4" t="n">
-        <v>89789</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -941,19 +922,20 @@
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tallåsen, Sävsjön, Ög</t>
+          <t>Tallåsen S, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>555989.5733167742</v>
+        <v>556047</v>
       </c>
       <c r="R4" t="n">
-        <v>6514802.641588474</v>
+        <v>6514729</v>
       </c>
       <c r="S4" t="n">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -977,22 +959,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2018-11-01</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2018-11-01</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,27 +980,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Suvi Bergström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Suvi Bergström, Marika Sjödin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>73809508</v>
+        <v>97390310</v>
       </c>
       <c r="B5" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1054,21 +1021,20 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tallåsen, Sävsjön, Ög</t>
+          <t>Häradstorp, Finspång, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>555989.5733167742</v>
+        <v>556042</v>
       </c>
       <c r="R5" t="n">
-        <v>6514802.641588474</v>
+        <v>6514711</v>
       </c>
       <c r="S5" t="n">
-        <v>104</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1092,22 +1058,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2018-11-01</t>
+          <t>2021-12-03</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2018-11-01</t>
+          <t>2021-12-03</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,34 +1082,28 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>73809509</v>
+        <v>113680727</v>
       </c>
       <c r="B6" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91995</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1151,39 +1111,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Tallåsen, Sävsjön, Ög</t>
+          <t>Tallåsen, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>555989.5733167742</v>
+        <v>556146</v>
       </c>
       <c r="R6" t="n">
-        <v>6514802.641588474</v>
+        <v>6514666</v>
       </c>
       <c r="S6" t="n">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1207,22 +1165,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2018-11-01</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2018-11-01</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1231,34 +1179,37 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>73862824</v>
+        <v>131740111</v>
       </c>
       <c r="B7" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91995</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1266,39 +1217,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Tallåsen, Sävsjön, Ög</t>
+          <t>Tallåsen Öst, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>555989.5733167742</v>
+        <v>555992</v>
       </c>
       <c r="R7" t="n">
-        <v>6514802.641588474</v>
+        <v>6514808</v>
       </c>
       <c r="S7" t="n">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1322,22 +1271,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2018-11-01</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2018-11-01</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1346,76 +1285,71 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Sanna Strömberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>79864635</v>
+        <v>103304778</v>
       </c>
       <c r="B8" t="n">
-        <v>8451</v>
+        <v>79084</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Tallåsen, Sävsjön, Ög</t>
+          <t>Finspång, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>555990</v>
+        <v>556032</v>
       </c>
       <c r="R8" t="n">
-        <v>6514803</v>
+        <v>6514710</v>
       </c>
       <c r="S8" t="n">
-        <v>104</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1439,12 +1373,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2019-09-10</t>
+          <t>2022-09-01</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2019-09-10</t>
+          <t>2022-09-01</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1453,34 +1397,28 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Staffan Carlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Staffan Carlsson, Torbjörn Blixt, Claud Youssif</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>79866032</v>
+        <v>103304677</v>
       </c>
       <c r="B9" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>6274</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1488,40 +1426,40 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>105336</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vanlig flatbagge</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Peltis ferruginea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Tallåsen, Sävsjön, Ög</t>
+          <t>Finspång, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>555989.5733167742</v>
+        <v>556041</v>
       </c>
       <c r="R9" t="n">
-        <v>6514802.641588474</v>
+        <v>6514667</v>
       </c>
       <c r="S9" t="n">
-        <v>104</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1545,22 +1483,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2019-09-10</t>
+          <t>2022-09-01</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2019-09-10</t>
+          <t>2022-09-01</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1569,79 +1507,73 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Staffan Carlsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Staffan Carlsson, Torbjörn Blixt</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>79938943</v>
+        <v>89159539</v>
       </c>
       <c r="B10" t="n">
-        <v>90697</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5449</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Tallåsen, Sävsjön, Ög</t>
+          <t>Häradstorp, Finspång, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>555989.5733167742</v>
+        <v>556077</v>
       </c>
       <c r="R10" t="n">
-        <v>6514802.641588474</v>
+        <v>6514730</v>
       </c>
       <c r="S10" t="n">
-        <v>104</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1665,22 +1597,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2019-09-08</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-11-20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2019-09-08</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-11-20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1689,7 +1611,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1701,22 +1622,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Marika Sjödin, Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>80856389</v>
+        <v>103304578</v>
       </c>
       <c r="B11" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>109815</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1724,40 +1640,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5966</v>
+        <v>220204</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Tallåsen, Sävsjön, Ög</t>
+          <t>Finspång, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>555989.5733167742</v>
+        <v>556070</v>
       </c>
       <c r="R11" t="n">
-        <v>6514802.641588474</v>
+        <v>6514635</v>
       </c>
       <c r="S11" t="n">
-        <v>104</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1781,22 +1696,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2019-10-23</t>
+          <t>2022-09-01</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2019-10-23</t>
+          <t>2022-09-01</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1805,900 +1720,21 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Staffan Carlsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Staffan Carlsson, Torbjörn Blixt, Claud Youssif</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>89159539</v>
-      </c>
-      <c r="B12" t="n">
-        <v>8451</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>106545</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Mindre märgborre</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Tomicus minor</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Häradstorp, Finspång, Ög</t>
-        </is>
-      </c>
-      <c r="Q12" t="n">
-        <v>556077</v>
-      </c>
-      <c r="R12" t="n">
-        <v>6514730</v>
-      </c>
-      <c r="S12" t="n">
-        <v>25</v>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>Finspång</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>Risinge</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>2020-11-20</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>2020-11-20</t>
-        </is>
-      </c>
-      <c r="AD12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="inlineStr"/>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>Marika Sjödin</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>Marika Sjödin, Eva Siljeholm</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>97390310</v>
-      </c>
-      <c r="B13" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>5442</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Tallticka</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Porodaedalea pini</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Häradstorp, Finspång, Ög</t>
-        </is>
-      </c>
-      <c r="Q13" t="n">
-        <v>556042.8595418548</v>
-      </c>
-      <c r="R13" t="n">
-        <v>6514711.085597772</v>
-      </c>
-      <c r="S13" t="n">
-        <v>25</v>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>Finspång</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>Risinge</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>2021-12-03</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>12:17</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>2021-12-03</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>12:17</t>
-        </is>
-      </c>
-      <c r="AD13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT13" t="inlineStr"/>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>103305058</v>
-      </c>
-      <c r="B14" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>353</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Dvärgbägarlav</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Cladonia parasitica</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Häradstorp, Finspång, Ög</t>
-        </is>
-      </c>
-      <c r="Q14" t="n">
-        <v>556068.8207546618</v>
-      </c>
-      <c r="R14" t="n">
-        <v>6514712.498541592</v>
-      </c>
-      <c r="S14" t="n">
-        <v>25</v>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>Finspång</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>Risinge</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>2022-09-01</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>13:52</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>2022-09-01</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>13:52</t>
-        </is>
-      </c>
-      <c r="AD14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT14" t="inlineStr"/>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>Staffan Carlsson</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>Staffan Carlsson, Torbjörn Blixt, Claud Youssif</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>103304778</v>
-      </c>
-      <c r="B15" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>6446</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Carbonicola anthracophila</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Finspång, Ög</t>
-        </is>
-      </c>
-      <c r="Q15" t="n">
-        <v>556031.964526344</v>
-      </c>
-      <c r="R15" t="n">
-        <v>6514709.890654637</v>
-      </c>
-      <c r="S15" t="n">
-        <v>25</v>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Finspång</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Risinge</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2022-09-01</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>13:42</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>2022-09-01</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>13:42</t>
-        </is>
-      </c>
-      <c r="AD15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="inlineStr"/>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>Staffan Carlsson</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>Staffan Carlsson, Torbjörn Blixt, Claud Youssif</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>103304626</v>
-      </c>
-      <c r="B16" t="n">
-        <v>89789</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>5420</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Grovticka</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Phaeolus schweinitzii</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Finspång, Ög</t>
-        </is>
-      </c>
-      <c r="Q16" t="n">
-        <v>556041.4189361196</v>
-      </c>
-      <c r="R16" t="n">
-        <v>6514666.97558204</v>
-      </c>
-      <c r="S16" t="n">
-        <v>25</v>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Finspång</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>Risinge</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2022-09-01</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>13:34</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>2022-09-01</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>13:34</t>
-        </is>
-      </c>
-      <c r="AD16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="inlineStr"/>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>Staffan Carlsson</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>Staffan Carlsson, Torbjörn Blixt, Claud Youssif</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>103304677</v>
-      </c>
-      <c r="B17" t="n">
-        <v>6202</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>105336</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Vanlig flatbagge</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Peltis ferruginea</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Finspång, Ög</t>
-        </is>
-      </c>
-      <c r="Q17" t="n">
-        <v>556041.4189361196</v>
-      </c>
-      <c r="R17" t="n">
-        <v>6514666.97558204</v>
-      </c>
-      <c r="S17" t="n">
-        <v>25</v>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Finspång</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Risinge</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>2022-09-01</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>13:34</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>2022-09-01</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>13:34</t>
-        </is>
-      </c>
-      <c r="AD17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="inlineStr"/>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>Staffan Carlsson</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>Staffan Carlsson, Torbjörn Blixt</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>117235212</v>
-      </c>
-      <c r="B18" t="n">
-        <v>90902</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>5420</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Grovticka</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Phaeolus schweinitzii</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Tallåsen S, Ög</t>
-        </is>
-      </c>
-      <c r="Q18" t="n">
-        <v>556047</v>
-      </c>
-      <c r="R18" t="n">
-        <v>6514729</v>
-      </c>
-      <c r="S18" t="n">
-        <v>10</v>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>Finspång</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>Risinge</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>2023-08-18</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>2023-08-18</t>
-        </is>
-      </c>
-      <c r="AD18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF18" t="inlineStr"/>
-      <c r="AG18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="inlineStr"/>
-      <c r="AW18" t="inlineStr">
-        <is>
-          <t>Suvi Sivula</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>Marika Sjödin, Suvi Sivula</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>131740111</v>
-      </c>
-      <c r="B19" t="n">
-        <v>91913</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>5442</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Tallticka</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Porodaedalea pini</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>Tallåsen Öst, Ög</t>
-        </is>
-      </c>
-      <c r="Q19" t="n">
-        <v>555992</v>
-      </c>
-      <c r="R19" t="n">
-        <v>6514808</v>
-      </c>
-      <c r="S19" t="n">
-        <v>10</v>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>Finspång</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>Risinge</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>2025-04-08</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>2025-04-08</t>
-        </is>
-      </c>
-      <c r="AD19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT19" t="inlineStr"/>
-      <c r="AW19" t="inlineStr">
-        <is>
-          <t>Helene Andersson</t>
-        </is>
-      </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>Sanna Strömberg</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 10676-2022 artfynd.xlsx
+++ b/artfynd/A 10676-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103305058</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -888,6 +898,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103304626</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -989,6 +1004,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117235212</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1097,6 +1117,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97390310</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1203,6 +1228,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113680727</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1304,6 +1334,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131740111</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1412,6 +1447,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103304778</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1522,6 +1562,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103304677</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1626,6 +1671,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89159539</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1735,8 +1785,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103304578</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>